--- a/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -663,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 52,91</t>
+          <t>36,84; 52,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,47; 53,45</t>
+          <t>40,29; 54,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,09; 44,52</t>
+          <t>31,06; 44,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 50,08</t>
+          <t>40,11; 74,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 42,97</t>
+          <t>28,35; 42,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 54,83</t>
+          <t>39,86; 54,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,1; 43,13</t>
+          <t>29,48; 43,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 48,07</t>
+          <t>47,58; 76,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 45,91</t>
+          <t>34,74; 45,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,24; 51,83</t>
+          <t>41,79; 51,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,08; 42,34</t>
+          <t>32,24; 42,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 42,6</t>
+          <t>48,08; 72,49</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,12; 66,37</t>
+          <t>55,96; 66,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,59; 70,26</t>
+          <t>59,02; 69,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,98; 75,28</t>
+          <t>64,46; 75,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 54,92</t>
+          <t>71,0; 94,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,69; 72,25</t>
+          <t>62,54; 72,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,8; 72,72</t>
+          <t>62,53; 72,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,98; 71,94</t>
+          <t>62,26; 72,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 43,97</t>
+          <t>69,99; 91,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,57; 67,61</t>
+          <t>60,78; 67,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,96; 70,11</t>
+          <t>62,99; 70,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,65; 71,86</t>
+          <t>64,44; 72,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,0; 44,99</t>
+          <t>74,84; 90,11</t>
         </is>
       </c>
     </row>
@@ -943,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,8; 72,32</t>
+          <t>58,23; 72,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,01; 77,16</t>
+          <t>64,51; 76,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,52; 76,59</t>
+          <t>65,86; 76,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 60,52</t>
+          <t>61,33; 87,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,72; 78,0</t>
+          <t>64,65; 78,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,23; 79,05</t>
+          <t>67,06; 79,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,97; 80,34</t>
+          <t>69,04; 80,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 48,64</t>
+          <t>71,09; 93,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,57; 73,27</t>
+          <t>64,4; 73,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,81; 76,58</t>
+          <t>67,69; 76,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,03; 76,79</t>
+          <t>68,51; 76,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 47,75</t>
+          <t>70,95; 88,36</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,1; 80,3</t>
+          <t>69,0; 80,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,94; 82,07</t>
+          <t>71,14; 82,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,9; 80,3</t>
+          <t>68,53; 80,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 51,57</t>
+          <t>63,36; 91,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,89; 78,9</t>
+          <t>68,15; 79,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 76,81</t>
+          <t>65,26; 77,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,09; 78,7</t>
+          <t>66,94; 78,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,68; 51,69</t>
+          <t>68,38; 89,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,44; 77,71</t>
+          <t>69,99; 77,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,19; 78,22</t>
+          <t>70,26; 78,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,16; 77,85</t>
+          <t>69,04; 77,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,71; 45,66</t>
+          <t>70,05; 87,44</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,51; 65,82</t>
+          <t>59,6; 66,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,23; 68,19</t>
+          <t>61,9; 68,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,1; 68,02</t>
+          <t>62,04; 68,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,82</t>
+          <t>69,78; 83,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,16; 67,32</t>
+          <t>60,91; 67,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,79</t>
+          <t>62,89; 68,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,87; 67,93</t>
+          <t>61,77; 67,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,06; 39,72</t>
+          <t>73,5; 84,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,38; 65,82</t>
+          <t>61,45; 65,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,63</t>
+          <t>63,41; 67,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,88; 67,16</t>
+          <t>62,75; 67,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,44</t>
+          <t>73,63; 82,62</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>45537</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65551</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47729</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9365</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37567</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67303</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42647</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11711</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>83104</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132854</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90376</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>21076</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>37476; 53541</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>57029; 76821</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39447; 56140</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6536; 12204</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30527; 45759</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>56778; 77606</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34903; 51109</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8778; 14203</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>72738; 95748</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>118697; 147112</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>79121; 103092</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>16702; 25185</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>141724</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>144059</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>136722</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23987</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>157786</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>173541</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>159127</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27798</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>299511</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>317600</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>295849</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>51784</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>129587; 152896</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>130987; 154947</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>125834; 146617</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20020; 26553</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>145977; 168294</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>159553; 184919</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>147465; 171498</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23608; 30872</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>282614; 313868</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>300507; 335463</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>278446; 311493</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>46346; 55802</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107513</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121784</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24363</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83002</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>110807</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>126089</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>30791</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>152557</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>218320</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>247872</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>55153</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>61742; 77288</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>97489; 115832</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112775; 131654</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19195; 27494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>74786; 90391</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>101383; 119463</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>116286; 135295</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>26210; 34335</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>142775; 162818</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>204631; 231178</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>232715; 260507</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>48367; 60235</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>118769</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118556</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114922</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19620</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>123247</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>117190</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>108129</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34293</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>242016</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>235745</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>223051</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>53912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>109487; 127102</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>109127; 126412</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105413; 123732</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15540; 22462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>113986; 133130</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>106658; 126054</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>99209; 116889</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>29094; 38259</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>228120; 253309</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>222606; 247671</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>208519; 234447</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>46984; 58649</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>375587</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>435678</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>421157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>77333</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>104593</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>777188</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>904518</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>857149</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>181926</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>356422; 394946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>413497; 454263</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>401597; 440376</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>69996; 84020</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>380118; 422228</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>447890; 490760</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>415013; 455541</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>96721; 111564</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>750925; 804747</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>875216; 931656</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>827832; 884042</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>170762; 191593</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,84; 52,64</t>
+          <t>36,5; 52,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,29; 54,27</t>
+          <t>39,22; 53,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,06; 44,2</t>
+          <t>30,83; 44,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,11; 74,9</t>
+          <t>38,9; 74,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,35; 42,49</t>
+          <t>27,91; 42,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,86; 54,48</t>
+          <t>40,7; 54,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 43,17</t>
+          <t>28,79; 42,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,58; 76,99</t>
+          <t>46,25; 77,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 45,73</t>
+          <t>33,8; 44,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,79; 51,8</t>
+          <t>42,18; 52,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,24; 42,01</t>
+          <t>32,29; 42,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,08; 72,49</t>
+          <t>48,47; 71,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,96; 66,02</t>
+          <t>55,89; 66,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,02; 69,82</t>
+          <t>59,49; 70,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,46; 75,1</t>
+          <t>64,66; 75,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,0; 94,17</t>
+          <t>70,1; 93,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,54; 72,1</t>
+          <t>62,59; 72,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,53; 72,47</t>
+          <t>62,56; 72,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,26; 72,4</t>
+          <t>61,5; 71,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,99; 91,53</t>
+          <t>68,5; 91,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,78; 67,5</t>
+          <t>60,59; 68,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,99; 70,31</t>
+          <t>63,08; 70,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,44; 72,09</t>
+          <t>64,95; 71,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,84; 90,11</t>
+          <t>74,61; 90,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,23; 72,89</t>
+          <t>57,91; 72,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,51; 76,64</t>
+          <t>64,96; 76,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,86; 76,88</t>
+          <t>65,23; 76,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,33; 87,85</t>
+          <t>63,98; 89,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,65; 78,14</t>
+          <t>64,93; 78,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,06; 79,02</t>
+          <t>66,67; 78,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,04; 80,32</t>
+          <t>69,02; 80,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,09; 93,12</t>
+          <t>70,67; 91,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,4; 73,44</t>
+          <t>63,59; 73,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,69; 76,47</t>
+          <t>67,51; 76,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,51; 76,69</t>
+          <t>69,15; 76,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,95; 88,36</t>
+          <t>71,09; 88,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,0; 80,1</t>
+          <t>69,43; 80,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,14; 82,41</t>
+          <t>71,42; 82,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,53; 80,44</t>
+          <t>68,55; 79,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,36; 91,58</t>
+          <t>64,03; 92,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,15; 79,59</t>
+          <t>67,79; 78,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,26; 77,12</t>
+          <t>65,87; 77,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,94; 78,87</t>
+          <t>66,53; 79,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,38; 89,92</t>
+          <t>69,04; 89,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,99; 77,71</t>
+          <t>70,2; 78,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,26; 78,17</t>
+          <t>70,3; 78,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,04; 77,63</t>
+          <t>69,14; 77,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,05; 87,44</t>
+          <t>71,65; 88,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,6; 66,04</t>
+          <t>59,76; 66,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,9; 68,0</t>
+          <t>62,21; 67,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,04</t>
+          <t>62,12; 68,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 83,76</t>
+          <t>69,12; 83,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,91; 67,66</t>
+          <t>61,26; 67,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,89; 68,9</t>
+          <t>62,72; 68,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,77; 67,8</t>
+          <t>61,91; 67,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,5; 84,78</t>
+          <t>73,8; 85,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,45; 65,85</t>
+          <t>61,26; 65,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,5</t>
+          <t>63,39; 67,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,75; 67,01</t>
+          <t>62,82; 67,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,63; 82,62</t>
+          <t>73,72; 83,08</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37476; 53541</t>
+          <t>37129; 53614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57029; 76821</t>
+          <t>55525; 75219</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39447; 56140</t>
+          <t>39160; 56088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6536; 12204</t>
+          <t>6339; 12112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30527; 45759</t>
+          <t>30054; 45804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56778; 77606</t>
+          <t>57973; 78188</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34903; 51109</t>
+          <t>34091; 50490</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8778; 14203</t>
+          <t>8531; 14385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72738; 95748</t>
+          <t>70784; 93891</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118697; 147112</t>
+          <t>119785; 147999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79121; 103092</t>
+          <t>79249; 103290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16702; 25185</t>
+          <t>16840; 24876</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129587; 152896</t>
+          <t>129425; 153452</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130987; 154947</t>
+          <t>132031; 156040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125834; 146617</t>
+          <t>126231; 146448</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20020; 26553</t>
+          <t>19766; 26285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>145977; 168294</t>
+          <t>146092; 169538</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>159553; 184919</t>
+          <t>159635; 184969</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>147465; 171498</t>
+          <t>145678; 169789</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23608; 30872</t>
+          <t>23104; 30778</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>282614; 313868</t>
+          <t>281747; 316254</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>300507; 335463</t>
+          <t>300926; 334526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>278446; 311493</t>
+          <t>280622; 310777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46346; 55802</t>
+          <t>46202; 55837</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61742; 77288</t>
+          <t>61399; 77116</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97489; 115832</t>
+          <t>98171; 116240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112775; 131654</t>
+          <t>111695; 130249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19195; 27494</t>
+          <t>20024; 27859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74786; 90391</t>
+          <t>75105; 90693</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101383; 119463</t>
+          <t>100789; 118990</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116286; 135295</t>
+          <t>116258; 135397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26210; 34335</t>
+          <t>26056; 33816</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>142775; 162818</t>
+          <t>140972; 163016</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>204631; 231178</t>
+          <t>204080; 230434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232715; 260507</t>
+          <t>234883; 260646</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48367; 60235</t>
+          <t>48457; 60443</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109487; 127102</t>
+          <t>110175; 128192</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>109127; 126412</t>
+          <t>109562; 126732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105413; 123732</t>
+          <t>105437; 123021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15540; 22462</t>
+          <t>15703; 22788</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>113986; 133130</t>
+          <t>113390; 131683</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106658; 126054</t>
+          <t>107669; 126477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99209; 116889</t>
+          <t>98593; 117193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29094; 38259</t>
+          <t>29373; 38175</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228120; 253309</t>
+          <t>228799; 254352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>222606; 247671</t>
+          <t>222736; 248921</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>208519; 234447</t>
+          <t>208804; 235443</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46984; 58649</t>
+          <t>48055; 59672</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>356422; 394946</t>
+          <t>357395; 395617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>413497; 454263</t>
+          <t>415593; 454096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>401597; 440376</t>
+          <t>402102; 441011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69996; 84020</t>
+          <t>69339; 83614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>380118; 422228</t>
+          <t>382268; 419985</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>447890; 490760</t>
+          <t>446708; 490247</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415013; 455541</t>
+          <t>415971; 454660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96721; 111564</t>
+          <t>97109; 111974</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750925; 804747</t>
+          <t>748592; 803506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>875216; 931656</t>
+          <t>874944; 933318</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>827832; 884042</t>
+          <t>828723; 884751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>170762; 191593</t>
+          <t>170971; 192659</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34,89%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63,3%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>44,77%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>37,58%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>57,47%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,5; 52,71</t>
+          <t>28,32; 42,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,22; 53,13</t>
+          <t>40,47; 54,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 44,16</t>
+          <t>29,1; 43,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,9; 74,33</t>
+          <t>47,82; 77,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,91; 42,54</t>
+          <t>37,17; 52,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,7; 54,89</t>
+          <t>39,47; 53,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 42,65</t>
+          <t>31,09; 44,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,25; 77,98</t>
+          <t>39,11; 73,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,8; 44,84</t>
+          <t>34,13; 45,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,18; 52,11</t>
+          <t>42,24; 51,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,29; 42,09</t>
+          <t>32,08; 42,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,47; 71,6</t>
+          <t>47,36; 70,76</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81,83%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>61,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>64,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>70,04%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>68,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>67,18%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,89; 66,26</t>
+          <t>62,69; 72,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,49; 70,31</t>
+          <t>62,8; 72,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,66; 75,02</t>
+          <t>61,98; 71,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,1; 93,22</t>
+          <t>65,94; 90,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,59; 72,64</t>
+          <t>56,12; 66,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,56; 72,49</t>
+          <t>59,59; 70,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,5; 71,68</t>
+          <t>64,98; 75,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,5; 91,25</t>
+          <t>70,34; 93,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 68,01</t>
+          <t>60,57; 67,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,08; 70,12</t>
+          <t>62,96; 70,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,95; 71,93</t>
+          <t>64,65; 71,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,61; 90,17</t>
+          <t>73,9; 89,3</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>65,6%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>71,14%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>71,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77,85%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,91; 72,73</t>
+          <t>64,72; 78,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,96; 76,91</t>
+          <t>66,23; 79,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,23; 76,06</t>
+          <t>68,97; 80,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,98; 89,02</t>
+          <t>69,37; 92,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,93; 78,41</t>
+          <t>57,8; 72,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,67; 78,71</t>
+          <t>65,01; 77,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,02; 80,38</t>
+          <t>65,52; 76,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,67; 91,71</t>
+          <t>60,2; 87,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,59; 73,53</t>
+          <t>63,57; 73,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,51; 76,22</t>
+          <t>67,81; 76,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,15; 76,73</t>
+          <t>69,03; 76,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,09; 88,67</t>
+          <t>70,01; 87,98</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80,03%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>74,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>77,29%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>74,72%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,43; 80,78</t>
+          <t>67,89; 78,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,42; 82,62</t>
+          <t>65,38; 76,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,55; 79,98</t>
+          <t>66,09; 78,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,03; 92,91</t>
+          <t>67,53; 88,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,79; 78,73</t>
+          <t>69,1; 80,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,87; 77,38</t>
+          <t>70,94; 82,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,53; 79,08</t>
+          <t>68,9; 80,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,04; 89,73</t>
+          <t>60,36; 90,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,2; 78,03</t>
+          <t>70,44; 77,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,3; 78,56</t>
+          <t>70,19; 78,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,14; 77,96</t>
+          <t>69,16; 77,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,65; 88,97</t>
+          <t>70,35; 87,21</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>65,83%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,76; 66,15</t>
+          <t>61,16; 67,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,21; 67,98</t>
+          <t>62,72; 68,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,12; 68,13</t>
+          <t>61,87; 67,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,12; 83,35</t>
+          <t>72,99; 84,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,26; 67,3</t>
+          <t>59,51; 65,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,83</t>
+          <t>62,23; 68,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,91; 67,67</t>
+          <t>62,1; 68,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,8; 85,09</t>
+          <t>67,41; 82,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,26; 65,75</t>
+          <t>61,38; 65,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,39; 67,62</t>
+          <t>63,41; 67,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,82; 67,07</t>
+          <t>62,88; 67,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,72; 83,08</t>
+          <t>72,72; 82,04</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37567</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67303</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42647</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>45537</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>65551</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>47729</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9365</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>37567</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67303</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42647</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>18195</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37129; 53614</t>
+          <t>30496; 46270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55525; 75219</t>
+          <t>57653; 78109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39160; 56088</t>
+          <t>34449; 51061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6339; 12112</t>
+          <t>7342; 11913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30054; 45804</t>
+          <t>37802; 53816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57973; 78188</t>
+          <t>55877; 75663</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34091; 50490</t>
+          <t>39482; 56540</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8531; 14385</t>
+          <t>5893; 11143</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70784; 93891</t>
+          <t>71465; 96139</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119785; 147999</t>
+          <t>119978; 147189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79249; 103290</t>
+          <t>78719; 103894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16840; 24876</t>
+          <t>14407; 21523</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157786</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>173541</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159127</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23850</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>141724</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>144059</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>136722</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23987</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>157786</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>173541</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>159127</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51784</t>
+          <t>45086</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129425; 153452</t>
+          <t>146311; 168636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132031; 156040</t>
+          <t>160248; 185548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126231; 146448</t>
+          <t>146811; 170403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19766; 26285</t>
+          <t>19218; 26465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>146092; 169538</t>
+          <t>129957; 153710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>159635; 184969</t>
+          <t>132240; 155933</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>145678; 169789</t>
+          <t>126844; 146967</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23104; 30778</t>
+          <t>17866; 23830</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>281747; 316254</t>
+          <t>281637; 314377</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>300926; 334526</t>
+          <t>300379; 334506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280622; 310777</t>
+          <t>279338; 310492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46202; 55837</t>
+          <t>40307; 48712</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>83002</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>110807</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126089</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29533</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>69555</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>107513</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>121784</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24363</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>83002</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>110807</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>126089</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55153</t>
+          <t>51846</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61399; 77116</t>
+          <t>74860; 90225</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98171; 116240</t>
+          <t>100121; 119509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111695; 130249</t>
+          <t>116170; 135324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20024; 27859</t>
+          <t>24671; 32885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75105; 90693</t>
+          <t>61291; 76686</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100789; 118990</t>
+          <t>98248; 116605</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116258; 135397</t>
+          <t>112196; 131146</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26056; 33816</t>
+          <t>17793; 25923</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>140972; 163016</t>
+          <t>140943; 162446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>204080; 230434</t>
+          <t>205002; 231519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>234883; 260646</t>
+          <t>234485; 260844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48457; 60443</t>
+          <t>45587; 57289</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>123247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117190</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108129</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33340</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>118769</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>118556</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>114922</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19620</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>123247</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>117190</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>108129</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>53476</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110175; 128192</t>
+          <t>113559; 131973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>109562; 126732</t>
+          <t>106856; 125546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105437; 123021</t>
+          <t>97943; 116633</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15703; 22788</t>
+          <t>28134; 36985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>113390; 131683</t>
+          <t>109645; 127423</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107669; 126477</t>
+          <t>108820; 125889</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98593; 117193</t>
+          <t>105968; 123510</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29373; 38175</t>
+          <t>15386; 23134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228799; 254352</t>
+          <t>229594; 253304</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>222736; 248921</t>
+          <t>222399; 247833</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>208804; 235443</t>
+          <t>208879; 235115</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48055; 59672</t>
+          <t>47239; 58563</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>629</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>357395; 395617</t>
+          <t>381638; 420087</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415593; 454096</t>
+          <t>446719; 489949</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>402102; 441011</t>
+          <t>415725; 456400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69339; 83614</t>
+          <t>88848; 103108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>382268; 419985</t>
+          <t>355869; 393637</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446708; 490247</t>
+          <t>415703; 455491</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415971; 454660</t>
+          <t>401981; 440299</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97109; 111974</t>
+          <t>64389; 78663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>748592; 803506</t>
+          <t>750086; 804351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>874944; 933318</t>
+          <t>875273; 933404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>828723; 884751</t>
+          <t>829481; 885929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>170971; 192659</t>
+          <t>157965; 178217</t>
         </is>
       </c>
     </row>
